--- a/output/Data and Chart Outputs/central_america_power_by_type.xlsx
+++ b/output/Data and Chart Outputs/central_america_power_by_type.xlsx
@@ -10,8 +10,10 @@
     <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Chart - El Salvador" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Costa Rica" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="El Salvador" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Chart - Puerto Rico" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Costa Rica" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="El Salvador" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Puerto Rico" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -159,6 +161,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -371,7 +374,7 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -403,6 +406,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -411,6 +415,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -441,6 +446,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -653,7 +659,7 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -685,6 +691,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -693,6 +700,292 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Puerto Rico power generation by type (to Apr/26)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Puerto Rico'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Puerto Rico'!$A$2:$A$65</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Puerto Rico'!$B$2:$B$65</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Puerto Rico'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Puerto Rico'!$A$2:$A$65</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Puerto Rico'!$C$2:$C$65</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Puerto Rico'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1BAF7A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Puerto Rico'!$A$2:$A$65</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Puerto Rico'!$D$2:$D$65</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Puerto Rico'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EDA100"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Puerto Rico'!$A$2:$A$65</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Puerto Rico'!$E$2:$E$65</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Puerto Rico'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="E87BA4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Puerto Rico'!$A$2:$A$65</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Puerto Rico'!$F$2:$F$65</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Puerto Rico'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="008300"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Puerto Rico'!$A$2:$A$65</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Puerto Rico'!$G$2:$G$65</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Puerto Rico'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="9A9A9A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Puerto Rico'!$A$2:$A$65</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Puerto Rico'!$H$2:$H$65</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="30"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <numFmt formatCode="mmm/yy" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="5"/>
+        <tickMarkSkip val="5"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>GWh per month</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -734,6 +1027,33 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10080000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1093,7 +1413,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Monthly. Costa Rica: 2021-01 to 2026-06; El Salvador: 2021-01 to 2025-12. Ember lags real time by one to several months (it varies by country); the weekly run picks up new months as they're released.</t>
+          <t>Monthly. Costa Rica: 2021-01 to 2026-06; El Salvador: 2021-01 to 2025-12; Puerto Rico: 2021-01 to 2026-04. Ember lags real time by one to several months (it varies by country); the weekly run picks up new months as they're released.</t>
         </is>
       </c>
     </row>
@@ -4518,6 +4838,1730 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Coal</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>680</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="n">
+        <v>310</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>44228</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>650</v>
+      </c>
+      <c r="D3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="n">
+        <v>290</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>44256</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>700</v>
+      </c>
+      <c r="D4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F4" t="n">
+        <v>300</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>44287</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>630</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" t="n">
+        <v>320</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>44317</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>710</v>
+      </c>
+      <c r="D6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" t="n">
+        <v>290</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>44348</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>860</v>
+      </c>
+      <c r="D7" t="n">
+        <v>20</v>
+      </c>
+      <c r="E7" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" t="n">
+        <v>160</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>44378</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>940</v>
+      </c>
+      <c r="D8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" t="n">
+        <v>30</v>
+      </c>
+      <c r="F8" t="n">
+        <v>260</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>44409</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>870</v>
+      </c>
+      <c r="D9" t="n">
+        <v>20</v>
+      </c>
+      <c r="E9" t="n">
+        <v>30</v>
+      </c>
+      <c r="F9" t="n">
+        <v>250</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>44440</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>640</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>30</v>
+      </c>
+      <c r="F10" t="n">
+        <v>280</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>44470</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>610</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F11" t="n">
+        <v>270</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>44501</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>280</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" t="n">
+        <v>260</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>380</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>360</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" t="n">
+        <v>210</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>380</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" t="n">
+        <v>150</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>44621</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>550</v>
+      </c>
+      <c r="D16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" t="n">
+        <v>30</v>
+      </c>
+      <c r="F16" t="n">
+        <v>290</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>44652</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>430</v>
+      </c>
+      <c r="D17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" t="n">
+        <v>280</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>44682</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>480</v>
+      </c>
+      <c r="D18" t="n">
+        <v>20</v>
+      </c>
+      <c r="E18" t="n">
+        <v>30</v>
+      </c>
+      <c r="F18" t="n">
+        <v>340</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>560</v>
+      </c>
+      <c r="D19" t="n">
+        <v>20</v>
+      </c>
+      <c r="E19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F19" t="n">
+        <v>320</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>44743</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>600</v>
+      </c>
+      <c r="D20" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F20" t="n">
+        <v>190</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>44774</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>650</v>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="n">
+        <v>20</v>
+      </c>
+      <c r="F21" t="n">
+        <v>210</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>460</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>20</v>
+      </c>
+      <c r="F22" t="n">
+        <v>170</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>44835</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>450</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="n">
+        <v>20</v>
+      </c>
+      <c r="F23" t="n">
+        <v>300</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>44866</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>510</v>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" t="n">
+        <v>250</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>370</v>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="n">
+        <v>20</v>
+      </c>
+      <c r="F25" t="n">
+        <v>270</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>500</v>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" t="n">
+        <v>280</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>44958</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>610</v>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F27" t="n">
+        <v>150</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>570</v>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="n">
+        <v>20</v>
+      </c>
+      <c r="F28" t="n">
+        <v>210</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>610</v>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="n">
+        <v>20</v>
+      </c>
+      <c r="F29" t="n">
+        <v>200</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>45047</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>610</v>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="n">
+        <v>20</v>
+      </c>
+      <c r="F30" t="n">
+        <v>280</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>690</v>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="n">
+        <v>20</v>
+      </c>
+      <c r="F31" t="n">
+        <v>270</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>710</v>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="n">
+        <v>20</v>
+      </c>
+      <c r="F32" t="n">
+        <v>190</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>45139</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>740</v>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" t="n">
+        <v>300</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>740</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>20</v>
+      </c>
+      <c r="F34" t="n">
+        <v>290</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>610</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>20</v>
+      </c>
+      <c r="F35" t="n">
+        <v>160</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>620</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" t="n">
+        <v>160</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>630</v>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="n">
+        <v>20</v>
+      </c>
+      <c r="F37" t="n">
+        <v>170</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>580</v>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="n">
+        <v>20</v>
+      </c>
+      <c r="F38" t="n">
+        <v>240</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>480</v>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="n">
+        <v>20</v>
+      </c>
+      <c r="F39" t="n">
+        <v>200</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>590</v>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="n">
+        <v>20</v>
+      </c>
+      <c r="F40" t="n">
+        <v>300</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>590</v>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="n">
+        <v>20</v>
+      </c>
+      <c r="F41" t="n">
+        <v>260</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B42" t="n">
+        <v>10</v>
+      </c>
+      <c r="C42" t="n">
+        <v>490</v>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="n">
+        <v>20</v>
+      </c>
+      <c r="F42" t="n">
+        <v>160</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" t="n">
+        <v>580</v>
+      </c>
+      <c r="D43" t="n">
+        <v>20</v>
+      </c>
+      <c r="E43" t="n">
+        <v>20</v>
+      </c>
+      <c r="F43" t="n">
+        <v>160</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="n">
+        <v>540</v>
+      </c>
+      <c r="D44" t="n">
+        <v>20</v>
+      </c>
+      <c r="E44" t="n">
+        <v>20</v>
+      </c>
+      <c r="F44" t="n">
+        <v>290</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C45" t="n">
+        <v>440</v>
+      </c>
+      <c r="D45" t="n">
+        <v>20</v>
+      </c>
+      <c r="E45" t="n">
+        <v>20</v>
+      </c>
+      <c r="F45" t="n">
+        <v>300</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B46" t="n">
+        <v>10</v>
+      </c>
+      <c r="C46" t="n">
+        <v>500</v>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="n">
+        <v>20</v>
+      </c>
+      <c r="F46" t="n">
+        <v>230</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B47" t="n">
+        <v>10</v>
+      </c>
+      <c r="C47" t="n">
+        <v>610</v>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="n">
+        <v>20</v>
+      </c>
+      <c r="F47" t="n">
+        <v>240</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" t="n">
+        <v>660</v>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F48" t="n">
+        <v>220</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" t="n">
+        <v>580</v>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="n">
+        <v>20</v>
+      </c>
+      <c r="F49" t="n">
+        <v>310</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" t="n">
+        <v>560</v>
+      </c>
+      <c r="D50" t="n">
+        <v>20</v>
+      </c>
+      <c r="E50" t="n">
+        <v>10</v>
+      </c>
+      <c r="F50" t="n">
+        <v>190</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" t="n">
+        <v>440</v>
+      </c>
+      <c r="D51" t="n">
+        <v>20</v>
+      </c>
+      <c r="E51" t="n">
+        <v>20</v>
+      </c>
+      <c r="F51" t="n">
+        <v>190</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="n">
+        <v>450</v>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="n">
+        <v>20</v>
+      </c>
+      <c r="F52" t="n">
+        <v>330</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" t="n">
+        <v>460</v>
+      </c>
+      <c r="D53" t="n">
+        <v>20</v>
+      </c>
+      <c r="E53" t="n">
+        <v>20</v>
+      </c>
+      <c r="F53" t="n">
+        <v>240</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" t="n">
+        <v>600</v>
+      </c>
+      <c r="D54" t="n">
+        <v>20</v>
+      </c>
+      <c r="E54" t="n">
+        <v>20</v>
+      </c>
+      <c r="F54" t="n">
+        <v>310</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" t="n">
+        <v>530</v>
+      </c>
+      <c r="D55" t="n">
+        <v>30</v>
+      </c>
+      <c r="E55" t="n">
+        <v>20</v>
+      </c>
+      <c r="F55" t="n">
+        <v>280</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" t="n">
+        <v>610</v>
+      </c>
+      <c r="D56" t="n">
+        <v>20</v>
+      </c>
+      <c r="E56" t="n">
+        <v>20</v>
+      </c>
+      <c r="F56" t="n">
+        <v>270</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" t="n">
+        <v>790</v>
+      </c>
+      <c r="D57" t="n">
+        <v>20</v>
+      </c>
+      <c r="E57" t="n">
+        <v>20</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" t="n">
+        <v>780</v>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="n">
+        <v>20</v>
+      </c>
+      <c r="F58" t="n">
+        <v>280</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" t="n">
+        <v>680</v>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F59" t="n">
+        <v>150</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" t="n">
+        <v>600</v>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="n">
+        <v>20</v>
+      </c>
+      <c r="F60" t="n">
+        <v>260</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="n">
+        <v>490</v>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="n">
+        <v>20</v>
+      </c>
+      <c r="F61" t="n">
+        <v>270</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" t="n">
+        <v>570</v>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="n">
+        <v>20</v>
+      </c>
+      <c r="F62" t="n">
+        <v>300</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" t="n">
+        <v>560</v>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="n">
+        <v>10</v>
+      </c>
+      <c r="F63" t="n">
+        <v>140</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" t="n">
+        <v>660</v>
+      </c>
+      <c r="D64" t="n">
+        <v>20</v>
+      </c>
+      <c r="E64" t="n">
+        <v>20</v>
+      </c>
+      <c r="F64" t="n">
+        <v>230</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" t="n">
+        <v>620</v>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="n">
+        <v>20</v>
+      </c>
+      <c r="F65" t="n">
+        <v>300</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>310</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -6614,7 +8658,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8898,4 +10942,2438 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Bioenergy_GWh</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Coal_GWh</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Gas_GWh</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Hydro_GWh</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Other Fossil_GWh</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Solar_GWh</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Wind_GWh</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Total_GWh</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Gas_for_power_est_mcm_per_day</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>310</v>
+      </c>
+      <c r="E2" t="n">
+        <v>680</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>380</v>
+      </c>
+      <c r="H2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>290</v>
+      </c>
+      <c r="E3" t="n">
+        <v>650</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>320</v>
+      </c>
+      <c r="H3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I3" t="n">
+        <v>20</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1300</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>300</v>
+      </c>
+      <c r="E4" t="n">
+        <v>700</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>410</v>
+      </c>
+      <c r="H4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1460</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>320</v>
+      </c>
+      <c r="E5" t="n">
+        <v>630</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>480</v>
+      </c>
+      <c r="H5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1470</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>290</v>
+      </c>
+      <c r="E6" t="n">
+        <v>710</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>550</v>
+      </c>
+      <c r="H6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>160</v>
+      </c>
+      <c r="E7" t="n">
+        <v>860</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>470</v>
+      </c>
+      <c r="H7" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>260</v>
+      </c>
+      <c r="E8" t="n">
+        <v>940</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>440</v>
+      </c>
+      <c r="H8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" t="n">
+        <v>20</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1690</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>250</v>
+      </c>
+      <c r="E9" t="n">
+        <v>870</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>590</v>
+      </c>
+      <c r="H9" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1760</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.32</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>280</v>
+      </c>
+      <c r="E10" t="n">
+        <v>640</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>710</v>
+      </c>
+      <c r="H10" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1670</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.04</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>270</v>
+      </c>
+      <c r="E11" t="n">
+        <v>610</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>730</v>
+      </c>
+      <c r="H11" t="n">
+        <v>20</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1640</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>260</v>
+      </c>
+      <c r="E12" t="n">
+        <v>280</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>990</v>
+      </c>
+      <c r="H12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1560</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>250</v>
+      </c>
+      <c r="E13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>830</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1490</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>210</v>
+      </c>
+      <c r="E14" t="n">
+        <v>360</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>810</v>
+      </c>
+      <c r="H14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I14" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1410</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>150</v>
+      </c>
+      <c r="E15" t="n">
+        <v>380</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>730</v>
+      </c>
+      <c r="H15" t="n">
+        <v>20</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1290</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>290</v>
+      </c>
+      <c r="E16" t="n">
+        <v>550</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>590</v>
+      </c>
+      <c r="H16" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" t="n">
+        <v>20</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1480</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>280</v>
+      </c>
+      <c r="E17" t="n">
+        <v>430</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>600</v>
+      </c>
+      <c r="H17" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" t="n">
+        <v>20</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>340</v>
+      </c>
+      <c r="E18" t="n">
+        <v>480</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>750</v>
+      </c>
+      <c r="H18" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" t="n">
+        <v>20</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1620</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>320</v>
+      </c>
+      <c r="E19" t="n">
+        <v>560</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>770</v>
+      </c>
+      <c r="H19" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" t="n">
+        <v>20</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1700</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>190</v>
+      </c>
+      <c r="E20" t="n">
+        <v>600</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>790</v>
+      </c>
+      <c r="H20" t="n">
+        <v>20</v>
+      </c>
+      <c r="I20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1620</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>210</v>
+      </c>
+      <c r="E21" t="n">
+        <v>650</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>800</v>
+      </c>
+      <c r="H21" t="n">
+        <v>20</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1690</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>170</v>
+      </c>
+      <c r="E22" t="n">
+        <v>460</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>620</v>
+      </c>
+      <c r="H22" t="n">
+        <v>20</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1270</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>300</v>
+      </c>
+      <c r="E23" t="n">
+        <v>450</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>760</v>
+      </c>
+      <c r="H23" t="n">
+        <v>20</v>
+      </c>
+      <c r="I23" t="n">
+        <v>10</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>250</v>
+      </c>
+      <c r="E24" t="n">
+        <v>510</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>670</v>
+      </c>
+      <c r="H24" t="n">
+        <v>20</v>
+      </c>
+      <c r="I24" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1460</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>270</v>
+      </c>
+      <c r="E25" t="n">
+        <v>370</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>740</v>
+      </c>
+      <c r="H25" t="n">
+        <v>20</v>
+      </c>
+      <c r="I25" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1410</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>280</v>
+      </c>
+      <c r="E26" t="n">
+        <v>500</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>530</v>
+      </c>
+      <c r="H26" t="n">
+        <v>20</v>
+      </c>
+      <c r="I26" t="n">
+        <v>10</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1340</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>150</v>
+      </c>
+      <c r="E27" t="n">
+        <v>610</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>430</v>
+      </c>
+      <c r="H27" t="n">
+        <v>20</v>
+      </c>
+      <c r="I27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1220</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>210</v>
+      </c>
+      <c r="E28" t="n">
+        <v>570</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>570</v>
+      </c>
+      <c r="H28" t="n">
+        <v>20</v>
+      </c>
+      <c r="I28" t="n">
+        <v>10</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1380</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>200</v>
+      </c>
+      <c r="E29" t="n">
+        <v>610</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>510</v>
+      </c>
+      <c r="H29" t="n">
+        <v>20</v>
+      </c>
+      <c r="I29" t="n">
+        <v>10</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>280</v>
+      </c>
+      <c r="E30" t="n">
+        <v>610</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>710</v>
+      </c>
+      <c r="H30" t="n">
+        <v>20</v>
+      </c>
+      <c r="I30" t="n">
+        <v>10</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1630</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>270</v>
+      </c>
+      <c r="E31" t="n">
+        <v>690</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>670</v>
+      </c>
+      <c r="H31" t="n">
+        <v>20</v>
+      </c>
+      <c r="I31" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1660</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>190</v>
+      </c>
+      <c r="E32" t="n">
+        <v>710</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>690</v>
+      </c>
+      <c r="H32" t="n">
+        <v>20</v>
+      </c>
+      <c r="I32" t="n">
+        <v>10</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1620</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>300</v>
+      </c>
+      <c r="E33" t="n">
+        <v>740</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>610</v>
+      </c>
+      <c r="H33" t="n">
+        <v>20</v>
+      </c>
+      <c r="I33" t="n">
+        <v>10</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1680</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.52</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>290</v>
+      </c>
+      <c r="E34" t="n">
+        <v>740</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>530</v>
+      </c>
+      <c r="H34" t="n">
+        <v>20</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1580</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>160</v>
+      </c>
+      <c r="E35" t="n">
+        <v>610</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>670</v>
+      </c>
+      <c r="H35" t="n">
+        <v>20</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1460</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>160</v>
+      </c>
+      <c r="E36" t="n">
+        <v>620</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>450</v>
+      </c>
+      <c r="H36" t="n">
+        <v>20</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1250</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>170</v>
+      </c>
+      <c r="E37" t="n">
+        <v>630</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>440</v>
+      </c>
+      <c r="H37" t="n">
+        <v>20</v>
+      </c>
+      <c r="I37" t="n">
+        <v>10</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1270</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>240</v>
+      </c>
+      <c r="E38" t="n">
+        <v>580</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>310</v>
+      </c>
+      <c r="H38" t="n">
+        <v>20</v>
+      </c>
+      <c r="I38" t="n">
+        <v>10</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1160</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>200</v>
+      </c>
+      <c r="E39" t="n">
+        <v>480</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>350</v>
+      </c>
+      <c r="H39" t="n">
+        <v>20</v>
+      </c>
+      <c r="I39" t="n">
+        <v>10</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1060</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>300</v>
+      </c>
+      <c r="E40" t="n">
+        <v>590</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>310</v>
+      </c>
+      <c r="H40" t="n">
+        <v>20</v>
+      </c>
+      <c r="I40" t="n">
+        <v>10</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1230</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>260</v>
+      </c>
+      <c r="E41" t="n">
+        <v>590</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>380</v>
+      </c>
+      <c r="H41" t="n">
+        <v>20</v>
+      </c>
+      <c r="I41" t="n">
+        <v>10</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1260</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>160</v>
+      </c>
+      <c r="E42" t="n">
+        <v>490</v>
+      </c>
+      <c r="F42" t="n">
+        <v>10</v>
+      </c>
+      <c r="G42" t="n">
+        <v>750</v>
+      </c>
+      <c r="H42" t="n">
+        <v>20</v>
+      </c>
+      <c r="I42" t="n">
+        <v>10</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1440</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>160</v>
+      </c>
+      <c r="E43" t="n">
+        <v>580</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>720</v>
+      </c>
+      <c r="H43" t="n">
+        <v>20</v>
+      </c>
+      <c r="I43" t="n">
+        <v>20</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>290</v>
+      </c>
+      <c r="E44" t="n">
+        <v>540</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>700</v>
+      </c>
+      <c r="H44" t="n">
+        <v>20</v>
+      </c>
+      <c r="I44" t="n">
+        <v>20</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1570</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>300</v>
+      </c>
+      <c r="E45" t="n">
+        <v>440</v>
+      </c>
+      <c r="F45" t="n">
+        <v>10</v>
+      </c>
+      <c r="G45" t="n">
+        <v>730</v>
+      </c>
+      <c r="H45" t="n">
+        <v>20</v>
+      </c>
+      <c r="I45" t="n">
+        <v>20</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1520</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>230</v>
+      </c>
+      <c r="E46" t="n">
+        <v>500</v>
+      </c>
+      <c r="F46" t="n">
+        <v>10</v>
+      </c>
+      <c r="G46" t="n">
+        <v>710</v>
+      </c>
+      <c r="H46" t="n">
+        <v>20</v>
+      </c>
+      <c r="I46" t="n">
+        <v>10</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1480</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>240</v>
+      </c>
+      <c r="E47" t="n">
+        <v>610</v>
+      </c>
+      <c r="F47" t="n">
+        <v>10</v>
+      </c>
+      <c r="G47" t="n">
+        <v>640</v>
+      </c>
+      <c r="H47" t="n">
+        <v>20</v>
+      </c>
+      <c r="I47" t="n">
+        <v>10</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1530</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>220</v>
+      </c>
+      <c r="E48" t="n">
+        <v>660</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>400</v>
+      </c>
+      <c r="H48" t="n">
+        <v>20</v>
+      </c>
+      <c r="I48" t="n">
+        <v>10</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K48" t="n">
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>310</v>
+      </c>
+      <c r="E49" t="n">
+        <v>580</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>350</v>
+      </c>
+      <c r="H49" t="n">
+        <v>20</v>
+      </c>
+      <c r="I49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1270</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>190</v>
+      </c>
+      <c r="E50" t="n">
+        <v>560</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>420</v>
+      </c>
+      <c r="H50" t="n">
+        <v>10</v>
+      </c>
+      <c r="I50" t="n">
+        <v>20</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>190</v>
+      </c>
+      <c r="E51" t="n">
+        <v>440</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>450</v>
+      </c>
+      <c r="H51" t="n">
+        <v>20</v>
+      </c>
+      <c r="I51" t="n">
+        <v>20</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1120</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>330</v>
+      </c>
+      <c r="E52" t="n">
+        <v>450</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>410</v>
+      </c>
+      <c r="H52" t="n">
+        <v>20</v>
+      </c>
+      <c r="I52" t="n">
+        <v>10</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1220</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>240</v>
+      </c>
+      <c r="E53" t="n">
+        <v>460</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>400</v>
+      </c>
+      <c r="H53" t="n">
+        <v>20</v>
+      </c>
+      <c r="I53" t="n">
+        <v>20</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1140</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>310</v>
+      </c>
+      <c r="E54" t="n">
+        <v>600</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>400</v>
+      </c>
+      <c r="H54" t="n">
+        <v>20</v>
+      </c>
+      <c r="I54" t="n">
+        <v>20</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>280</v>
+      </c>
+      <c r="E55" t="n">
+        <v>530</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>540</v>
+      </c>
+      <c r="H55" t="n">
+        <v>20</v>
+      </c>
+      <c r="I55" t="n">
+        <v>30</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>270</v>
+      </c>
+      <c r="E56" t="n">
+        <v>610</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>570</v>
+      </c>
+      <c r="H56" t="n">
+        <v>20</v>
+      </c>
+      <c r="I56" t="n">
+        <v>20</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1490</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>790</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>430</v>
+      </c>
+      <c r="H57" t="n">
+        <v>20</v>
+      </c>
+      <c r="I57" t="n">
+        <v>20</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1260</v>
+      </c>
+      <c r="K57" t="n">
+        <v>4.83</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>280</v>
+      </c>
+      <c r="E58" t="n">
+        <v>780</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>390</v>
+      </c>
+      <c r="H58" t="n">
+        <v>20</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1480</v>
+      </c>
+      <c r="K58" t="n">
+        <v>4.93</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>150</v>
+      </c>
+      <c r="E59" t="n">
+        <v>680</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>660</v>
+      </c>
+      <c r="H59" t="n">
+        <v>20</v>
+      </c>
+      <c r="I59" t="n">
+        <v>10</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1520</v>
+      </c>
+      <c r="K59" t="n">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>260</v>
+      </c>
+      <c r="E60" t="n">
+        <v>600</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>510</v>
+      </c>
+      <c r="H60" t="n">
+        <v>20</v>
+      </c>
+      <c r="I60" t="n">
+        <v>10</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>270</v>
+      </c>
+      <c r="E61" t="n">
+        <v>490</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>540</v>
+      </c>
+      <c r="H61" t="n">
+        <v>20</v>
+      </c>
+      <c r="I61" t="n">
+        <v>10</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1330</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>300</v>
+      </c>
+      <c r="E62" t="n">
+        <v>570</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>350</v>
+      </c>
+      <c r="H62" t="n">
+        <v>20</v>
+      </c>
+      <c r="I62" t="n">
+        <v>10</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1250</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>140</v>
+      </c>
+      <c r="E63" t="n">
+        <v>560</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>380</v>
+      </c>
+      <c r="H63" t="n">
+        <v>10</v>
+      </c>
+      <c r="I63" t="n">
+        <v>10</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>230</v>
+      </c>
+      <c r="E64" t="n">
+        <v>660</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>310</v>
+      </c>
+      <c r="H64" t="n">
+        <v>20</v>
+      </c>
+      <c r="I64" t="n">
+        <v>20</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1240</v>
+      </c>
+      <c r="K64" t="n">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>300</v>
+      </c>
+      <c r="E65" t="n">
+        <v>620</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>310</v>
+      </c>
+      <c r="H65" t="n">
+        <v>20</v>
+      </c>
+      <c r="I65" t="n">
+        <v>10</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1260</v>
+      </c>
+      <c r="K65" t="n">
+        <v>3.92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/Data and Chart Outputs/central_america_power_by_type.xlsx
+++ b/output/Data and Chart Outputs/central_america_power_by_type.xlsx
@@ -22,8 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mmm/yy"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,11 +64,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -379,6 +379,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -412,6 +424,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -664,6 +682,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -697,6 +727,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -949,6 +985,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -982,6 +1030,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -1403,6 +1457,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -1417,6 +1472,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -1491,7 +1547,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1517,7 +1573,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1543,7 +1599,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1569,7 +1625,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1595,7 +1651,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1621,7 +1677,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1647,7 +1703,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1673,7 +1729,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1699,7 +1755,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1725,7 +1781,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1751,7 +1807,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1777,7 +1833,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1803,7 +1859,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1829,7 +1885,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1855,7 +1911,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1881,7 +1937,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1907,7 +1963,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1933,7 +1989,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1959,7 +2015,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1985,7 +2041,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -2011,7 +2067,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -2037,7 +2093,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -2063,7 +2119,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -2089,7 +2145,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -2115,7 +2171,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -2141,7 +2197,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -2167,7 +2223,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -2193,7 +2249,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -2219,7 +2275,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -2245,7 +2301,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -2271,7 +2327,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -2297,7 +2353,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -2323,7 +2379,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -2349,7 +2405,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -2375,7 +2431,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -2401,7 +2457,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2427,7 +2483,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2453,7 +2509,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2479,7 +2535,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2505,7 +2561,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2531,7 +2587,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2557,7 +2613,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2583,7 +2639,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2609,7 +2665,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2635,7 +2691,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2661,7 +2717,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2687,7 +2743,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2713,7 +2769,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2739,7 +2795,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2765,7 +2821,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2791,7 +2847,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2817,7 +2873,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2843,7 +2899,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2869,7 +2925,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2895,7 +2951,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2921,7 +2977,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2947,7 +3003,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2973,7 +3029,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2999,7 +3055,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -3025,7 +3081,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -3051,7 +3107,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -3077,7 +3133,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -3103,7 +3159,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -3129,7 +3185,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -3155,7 +3211,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -3181,7 +3237,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -3267,7 +3323,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -3293,7 +3349,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -3319,7 +3375,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -3345,7 +3401,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -3371,7 +3427,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -3397,7 +3453,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -3423,7 +3479,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -3449,7 +3505,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -3475,7 +3531,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -3501,7 +3557,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -3527,7 +3583,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -3553,7 +3609,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -3579,7 +3635,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -3605,7 +3661,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -3631,7 +3687,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -3657,7 +3713,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -3683,7 +3739,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -3709,7 +3765,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -3735,7 +3791,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -3761,7 +3817,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -3787,7 +3843,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -3813,7 +3869,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -3839,7 +3895,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -3865,7 +3921,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -3891,7 +3947,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -3917,7 +3973,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -3943,7 +3999,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -3969,7 +4025,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -3995,7 +4051,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -4021,7 +4077,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -4047,7 +4103,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -4073,7 +4129,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -4099,7 +4155,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -4125,7 +4181,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -4151,7 +4207,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -4177,7 +4233,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -4203,7 +4259,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -4229,7 +4285,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -4255,7 +4311,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -4281,7 +4337,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -4307,7 +4363,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -4333,7 +4389,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -4359,7 +4415,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -4385,7 +4441,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -4411,7 +4467,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -4437,7 +4493,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -4463,7 +4519,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -4489,7 +4545,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -4515,7 +4571,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -4541,7 +4597,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -4567,7 +4623,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -4593,7 +4649,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -4619,7 +4675,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -4645,7 +4701,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -4671,7 +4727,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -4697,7 +4753,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -4723,7 +4779,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -4749,7 +4805,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -4775,7 +4831,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -4801,7 +4857,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -4887,7 +4943,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -4913,7 +4969,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -4939,7 +4995,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -4965,7 +5021,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -4991,7 +5047,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -5017,7 +5073,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -5043,7 +5099,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -5069,7 +5125,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -5095,7 +5151,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -5121,7 +5177,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -5147,7 +5203,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -5173,7 +5229,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -5199,7 +5255,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -5225,7 +5281,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -5251,7 +5307,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -5277,7 +5333,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -5303,7 +5359,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -5329,7 +5385,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -5355,7 +5411,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -5381,7 +5437,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -5407,7 +5463,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -5433,7 +5489,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -5459,7 +5515,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -5485,7 +5541,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -5511,7 +5567,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -5537,7 +5593,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -5563,7 +5619,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -5589,7 +5645,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -5615,7 +5671,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -5641,7 +5697,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -5667,7 +5723,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -5693,7 +5749,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -5719,7 +5775,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -5745,7 +5801,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -5771,7 +5827,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -5797,7 +5853,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -5823,7 +5879,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -5849,7 +5905,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -5875,7 +5931,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -5901,7 +5957,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -5927,7 +5983,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -5953,7 +6009,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -5979,7 +6035,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -6005,7 +6061,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -6031,7 +6087,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -6057,7 +6113,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -6083,7 +6139,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -6109,7 +6165,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -6135,7 +6191,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -6161,7 +6217,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -6187,7 +6243,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -6213,7 +6269,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -6239,7 +6295,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -6265,7 +6321,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -6291,7 +6347,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -6317,7 +6373,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -6343,7 +6399,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -6369,7 +6425,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -6395,7 +6451,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -6421,7 +6477,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -6447,7 +6503,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -6473,7 +6529,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -6499,7 +6555,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -6525,7 +6581,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">

--- a/output/Data and Chart Outputs/central_america_power_by_type.xlsx
+++ b/output/Data and Chart Outputs/central_america_power_by_type.xlsx
@@ -156,6 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Costa Rica power generation by type (to Jun/26)</a:t>
             </a:r>
           </a:p>
@@ -459,6 +460,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>El Salvador power generation by type (to Dec/25)</a:t>
             </a:r>
           </a:p>
@@ -762,6 +764,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Puerto Rico power generation by type (to Apr/26)</a:t>
             </a:r>
           </a:p>
@@ -1468,7 +1471,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Monthly. Costa Rica: 2021-01 to 2026-06; El Salvador: 2021-01 to 2025-12; Puerto Rico: 2021-01 to 2026-04. Ember lags real time by one to several months (it varies by country); the weekly run picks up new months as they're released.</t>
+          <t>Monthly. Costa Rica: 2021-01 to 2026-06; El Salvador: 2021-01 to 2025-12; Puerto Rico: 2021-01 to 2026-04. Ember lags real time by one to several months (it varies by country); each scheduled run picks up new months as they're released.</t>
         </is>
       </c>
     </row>
